--- a/artfynd/A 13065-2026 artfynd.xlsx
+++ b/artfynd/A 13065-2026 artfynd.xlsx
@@ -2195,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133673704</v>
+        <v>133673722</v>
       </c>
       <c r="B15" t="n">
-        <v>97657</v>
+        <v>97741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2563</v>
+        <v>2326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133673722</v>
+        <v>133673704</v>
       </c>
       <c r="B16" t="n">
-        <v>97741</v>
+        <v>97657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,21 +2318,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2326</v>
+        <v>2563</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 13065-2026 artfynd.xlsx
+++ b/artfynd/A 13065-2026 artfynd.xlsx
@@ -2198,7 +2198,7 @@
         <v>133673722</v>
       </c>
       <c r="B15" t="n">
-        <v>97741</v>
+        <v>97748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>133673704</v>
       </c>
       <c r="B16" t="n">
-        <v>97657</v>
+        <v>97664</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>133673715</v>
       </c>
       <c r="B17" t="n">
-        <v>97839</v>
+        <v>97846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 13065-2026 artfynd.xlsx
+++ b/artfynd/A 13065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53552678</v>
+        <v>65018902</v>
       </c>
       <c r="B2" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1590</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laxemossen, Dls</t>
+          <t>Sydväst Hollstens grustag, Hollsten,  Laxarby, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353448.2506826456</v>
+        <v>353467</v>
       </c>
       <c r="R2" t="n">
-        <v>6556627.452578465</v>
+        <v>6556751</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Källpåverkad mark i kanten mot österut liggande sluttning/fastmark</t>
+          <t>Granlåga i norra kanten av gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,53 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65018933</v>
+        <v>100693768</v>
       </c>
       <c r="B3" t="n">
-        <v>92683</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2383</v>
+        <v>771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Laxemossen, Dls</t>
+          <t>Laxetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>353448.2506826456</v>
+        <v>353416</v>
       </c>
       <c r="R3" t="n">
-        <v>6556627.452578465</v>
+        <v>6556645</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -876,22 +845,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-18</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-18</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mossornas vänners vårexkursion</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,53 +880,56 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enfjäll, Sigrid Bruvoll</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70773581</v>
+        <v>53552678</v>
       </c>
       <c r="B4" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>1590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -961,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>353448.2506826456</v>
+        <v>353448</v>
       </c>
       <c r="R4" t="n">
-        <v>6556627.452578465</v>
+        <v>6556627</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -991,22 +968,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Källpåverkad mark i kanten mot österut liggande sluttning/fastmark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,56 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70773578</v>
+        <v>100693783</v>
       </c>
       <c r="B5" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>1590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxemossen, Dls</t>
+          <t>Laxetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>353448.2506826456</v>
+        <v>353407</v>
       </c>
       <c r="R5" t="n">
-        <v>6556627.452578465</v>
+        <v>6556627</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1070,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mossornas vänners vårexkursion</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,68 +1105,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65018950</v>
+        <v>133673715</v>
       </c>
       <c r="B6" t="n">
-        <v>94764</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2326</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Laxemossen, Dls</t>
+          <t>Laxetjärnet V Korpflåget, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>353448.2506826456</v>
+        <v>353433</v>
       </c>
       <c r="R6" t="n">
-        <v>6556627.452578465</v>
+        <v>6556648</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-04-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-04-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,33 +1200,39 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Emma Enfjäll, Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100693777</v>
+        <v>65018950</v>
       </c>
       <c r="B7" t="n">
-        <v>94764</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,19 +1258,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Laxetjärnet, Dls</t>
+          <t>Laxemossen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>353407.070883043</v>
+        <v>353448</v>
       </c>
       <c r="R7" t="n">
-        <v>6556627.491724044</v>
+        <v>6556627</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,27 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mossornas vänners vårexkursion</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,34 +1311,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Stork, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnus</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100693778</v>
+        <v>100693767</v>
       </c>
       <c r="B8" t="n">
-        <v>94653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1340,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2563</v>
+        <v>2326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>353407.070883043</v>
+        <v>353416</v>
       </c>
       <c r="R8" t="n">
-        <v>6556627.491724044</v>
+        <v>6556645</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,22 +1434,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Stork, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnus</t>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Andersson, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100693767</v>
+        <v>100693777</v>
       </c>
       <c r="B9" t="n">
-        <v>94764</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,13 +1476,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>353415.9647304317</v>
+        <v>353407</v>
       </c>
       <c r="R9" t="n">
-        <v>6556644.621301726</v>
+        <v>6556627</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,6 +1535,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1608,60 +1547,59 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Stork, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnus</t>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Andersson, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100693768</v>
+        <v>133673722</v>
       </c>
       <c r="B10" t="n">
-        <v>93160</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>771</v>
+        <v>2326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Laxetjärnet, Dls</t>
+          <t>Laxetjärnet V Korpflåget, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>353415.9647304317</v>
+        <v>353402</v>
       </c>
       <c r="R10" t="n">
-        <v>6556644.621301726</v>
+        <v>6556621</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,27 +1623,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mossornas vänners vårexkursion</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,33 +1637,39 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enfjäll, Sigrid Br</t>
+          <t>Emma Enfjäll, Anton Björk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100693783</v>
+        <v>65018933</v>
       </c>
       <c r="B11" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,37 +1677,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1590</v>
+        <v>2383</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Laxetjärnet, Dls</t>
+          <t>Laxemossen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>353407.070883043</v>
+        <v>353448</v>
       </c>
       <c r="R11" t="n">
-        <v>6556627.491724044</v>
+        <v>6556627</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,27 +1734,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mossornas vänners vårexkursion</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,27 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enf</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100693786</v>
+        <v>100693778</v>
       </c>
       <c r="B12" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>97594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2813</v>
+        <v>2563</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>353407.070883043</v>
+        <v>353407</v>
       </c>
       <c r="R12" t="n">
-        <v>6556627.491724044</v>
+        <v>6556627</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1959,22 +1871,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Stork, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnus</t>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Andersson, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100693789</v>
+        <v>119691495</v>
       </c>
       <c r="B13" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,37 +1889,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>2563</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Terpentinmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Geocalyx graveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schrad.) Nees</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Laxetjärnet, Dls</t>
+          <t>Laxemossen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>353407.070883043</v>
+        <v>353448</v>
       </c>
       <c r="R13" t="n">
-        <v>6556627.491724044</v>
+        <v>6556627</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,27 +1947,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Mossornas vänners vårexkursion</t>
+          <t>På trädbaser i sumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,33 +1966,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sara Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enf</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119691495</v>
+        <v>133673704</v>
       </c>
       <c r="B14" t="n">
-        <v>96012</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,17 +2020,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Laxemossen, Dls</t>
+          <t>Laxetjärnet V Korpflåget, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>353448</v>
+        <v>353402</v>
       </c>
       <c r="R14" t="n">
-        <v>6556627</v>
+        <v>6556621</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,17 +2054,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På trädbaser i sumpskog</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,25 +2072,35 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog med klibbal.</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Emma Enfjäll, Anton Björk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133673722</v>
+        <v>70773581</v>
       </c>
       <c r="B15" t="n">
-        <v>97748</v>
+        <v>97733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,41 +2108,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2326</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Laxetjärnet V Korpflåget, Dls</t>
+          <t>Laxemossen, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>353402</v>
+        <v>353448</v>
       </c>
       <c r="R15" t="n">
-        <v>6556621</v>
+        <v>6556627</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,12 +2165,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,81 +2179,69 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gammal gransumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emma Enfjäll, Anton Björk</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133673704</v>
+        <v>65018916</v>
       </c>
       <c r="B16" t="n">
-        <v>97664</v>
+        <v>97844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2563</v>
+        <v>2617</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Laxetjärnet V Korpflåget, Dls</t>
+          <t>Sydväst Hollstens grustag, Hollsten,  Laxarby, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>353402</v>
+        <v>353467</v>
       </c>
       <c r="R16" t="n">
-        <v>6556621</v>
+        <v>6556751</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,12 +2265,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2017-04-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,39 +2279,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal gransumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Enfjäll, Anton Björk</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133673715</v>
+        <v>70773578</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>96338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,41 +2308,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1590</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Laxetjärnet V Korpflåget, Dls</t>
+          <t>Laxemossen, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>353433</v>
+        <v>353448</v>
       </c>
       <c r="R17" t="n">
-        <v>6556648</v>
+        <v>6556627</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,12 +2365,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,32 +2379,359 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal gransumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Enfjäll, Anton Björk</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100693786</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Laxetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>353407</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556627</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Mossornas vänners vårexkursion</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Johan Andersson, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73354550</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Laxemossen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>353448</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556627</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gick på grusvägen</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100693789</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Laxetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>353407</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556627</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laxarby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mossornas vänners vårexkursion</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors, Tomas Hallingbäck, Marie Glahn, Fredrik Larsson, Roger Gran, Åke Berg, Niklas Hjort, Marika Sjödin, Staffan Carlsson, Per Darell, Bent Odgaard, Anders Niklasson, Sarah Asker, Carl-Axel Andersson, Henrik Ekstrand, Magnus J Magnusson, Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13065-2026 artfynd.xlsx
+++ b/artfynd/A 13065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65018902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53552678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693783</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133673715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65018950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693767</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693777</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133673722</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65018933</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693778</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119691495</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2094,6 +2159,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133673704</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,6 +2264,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70773581</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65018916</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70773578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693786</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2620,6 +2710,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73354550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,8 +2827,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100693789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>